--- a/Asset/Tableau_synthese_E5_ZIANI_Samir.xlsx
+++ b/Asset/Tableau_synthese_E5_ZIANI_Samir.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samir\Documents\SAMIR\BTS SIO\Dev\Présentation Oral E5\Prépa exam blanc\portfolio\Asset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samir\Documents\SAMIR\BTS SIO\Dev\Présentation Oral E5\Prepa Exam Blanc - Portfolio\Asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DDFDA3-2E95-4747-A4EB-99F04364DFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5888B055-AA01-435B-B6BD-16F0FBABBEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -697,25 +697,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -736,6 +722,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1056,50 +1056,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="31"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:13" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="36" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="40" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="28"/>
@@ -1117,22 +1117,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="33" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1155,8 +1155,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="20" t="s">
         <v>18</v>
       </c>
@@ -1177,16 +1177,16 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="42"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
@@ -1319,7 +1319,7 @@
       <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="27" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="28"/>
@@ -1417,7 +1417,7 @@
       <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:8" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="27" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="28"/>
@@ -1510,6 +1510,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
@@ -1517,11 +1522,6 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
